--- a/JsonConverter/ExcelFiles/LandUpGradeData.xlsx
+++ b/JsonConverter/ExcelFiles/LandUpGradeData.xlsx
@@ -61,25 +61,25 @@
     <t>LandUpGrade_02</t>
   </si>
   <si>
-    <t>Building_02_Shop</t>
+    <t>Building_05_Drug_Store</t>
   </si>
   <si>
     <t>LandUpGrade_03</t>
   </si>
   <si>
-    <t>Building_03_Museum</t>
+    <t>Building_07_Apartment</t>
   </si>
   <si>
     <t>LandUpGrade_04</t>
   </si>
   <si>
-    <t>Building_04_Fitness_Center</t>
+    <t>Building_09_Cinema</t>
   </si>
   <si>
     <t>LandUpGrade_05</t>
   </si>
   <si>
-    <t>Building_05_Theater</t>
+    <t>Building_11_Police_Office</t>
   </si>
 </sst>
 </file>
@@ -127,9 +127,6 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -140,6 +137,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -383,18 +383,18 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="3"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="2"/>
     </row>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D2" s="1" t="s">
@@ -403,12 +403,12 @@
       <c r="E2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="4"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="3"/>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -423,9 +423,9 @@
       <c r="E3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="4"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="3"/>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
@@ -440,112 +440,112 @@
       <c r="D4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="5"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="4"/>
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="1">
-        <v>200.0</v>
+      <c r="B5" s="5">
+        <v>1000.0</v>
       </c>
       <c r="C5" s="1">
         <v>5.0</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="5"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="4"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="1">
-        <v>500.0</v>
-      </c>
-      <c r="C6" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="D6" s="1" t="s">
+      <c r="B6" s="5">
+        <v>5000.0</v>
+      </c>
+      <c r="C6" s="5">
+        <v>20.0</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="5"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="4"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="1">
-        <v>1000.0</v>
+      <c r="B7" s="5">
+        <v>7500.0</v>
       </c>
       <c r="C7" s="1">
         <v>50.0</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="5"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="4"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="1">
-        <v>10000.0</v>
+      <c r="B8" s="5">
+        <v>12000.0</v>
       </c>
       <c r="C8" s="1">
         <v>100.0</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="5"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="4"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="5"/>
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="4"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="2"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
+      <c r="A10" s="1"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
     </row>
     <row r="12" ht="15.75" customHeight="1"/>
     <row r="13" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/LandUpGradeData.xlsx
+++ b/JsonConverter/ExcelFiles/LandUpGradeData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
   <si>
     <t>고유 ID</t>
   </si>
@@ -62,6 +62,9 @@
   </si>
   <si>
     <t>Building_05_Drug_Store</t>
+  </si>
+  <si>
+    <t>Cat_Normal_01</t>
   </si>
   <si>
     <t>LandUpGrade_03</t>
@@ -449,32 +452,34 @@
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="1">
         <v>1000.0</v>
       </c>
       <c r="C5" s="1">
         <v>5.0</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="1"/>
+      <c r="E5" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="4"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="5">
+        <v>18</v>
+      </c>
+      <c r="B6" s="1">
         <v>5000.0</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="1">
         <v>20.0</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>18</v>
+      <c r="D6" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
@@ -483,16 +488,16 @@
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="5">
+        <v>20</v>
+      </c>
+      <c r="B7" s="1">
         <v>7500.0</v>
       </c>
       <c r="C7" s="1">
         <v>50.0</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>20</v>
+      <c r="D7" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
@@ -501,16 +506,16 @@
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="5">
+        <v>22</v>
+      </c>
+      <c r="B8" s="1">
         <v>12000.0</v>
       </c>
       <c r="C8" s="1">
         <v>100.0</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>22</v>
+      <c r="D8" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>

--- a/JsonConverter/ExcelFiles/LandUpGradeData.xlsx
+++ b/JsonConverter/ExcelFiles/LandUpGradeData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
   <si>
     <t>고유 ID</t>
   </si>
@@ -58,13 +58,16 @@
     <t>Building_01_House</t>
   </si>
   <si>
+    <t>Cat_Normal_01</t>
+  </si>
+  <si>
     <t>LandUpGrade_02</t>
   </si>
   <si>
     <t>Building_05_Drug_Store</t>
   </si>
   <si>
-    <t>Cat_Normal_01</t>
+    <t>Cat_Special_03</t>
   </si>
   <si>
     <t>LandUpGrade_03</t>
@@ -73,16 +76,25 @@
     <t>Building_07_Apartment</t>
   </si>
   <si>
+    <t>Cat_Special_07</t>
+  </si>
+  <si>
     <t>LandUpGrade_04</t>
   </si>
   <si>
     <t>Building_09_Cinema</t>
   </si>
   <si>
+    <t>Cat_Special_02</t>
+  </si>
+  <si>
     <t>LandUpGrade_05</t>
   </si>
   <si>
     <t>Building_11_Police_Office</t>
+  </si>
+  <si>
+    <t>Cat_Special_04</t>
   </si>
 </sst>
 </file>
@@ -138,11 +150,11 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -443,14 +455,16 @@
       <c r="D4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="1"/>
+      <c r="E4" s="4" t="s">
+        <v>15</v>
+      </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="4"/>
+      <c r="H4" s="5"/>
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B5" s="1">
         <v>1000.0</v>
@@ -459,18 +473,18 @@
         <v>5.0</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="5" t="s">
         <v>17</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
-      <c r="H5" s="4"/>
+      <c r="H5" s="5"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B6" s="1">
         <v>5000.0</v>
@@ -479,16 +493,18 @@
         <v>20.0</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="1"/>
+        <v>20</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
-      <c r="H6" s="4"/>
+      <c r="H6" s="5"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B7" s="1">
         <v>7500.0</v>
@@ -497,16 +513,18 @@
         <v>50.0</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="1"/>
+        <v>23</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>24</v>
+      </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
-      <c r="H7" s="4"/>
+      <c r="H7" s="5"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B8" s="1">
         <v>12000.0</v>
@@ -515,12 +533,14 @@
         <v>100.0</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>27</v>
+      </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
-      <c r="H8" s="4"/>
+      <c r="H8" s="5"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="1"/>
@@ -530,27 +550,27 @@
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
-      <c r="H9" s="4"/>
+      <c r="H9" s="5"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="3"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
     </row>
     <row r="12" ht="15.75" customHeight="1"/>
     <row r="13" ht="15.75" customHeight="1"/>
